--- a/Eszközök/Forrás/2-14.b.xlsx
+++ b/Eszközök/Forrás/2-14.b.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20402"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bence\Dokumentumok\Visual Studio 2022\Repos\GitHub\IskolaAPI\IskolaAPI2\Feladat\Forrás\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\boros.bence\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA04FC10-B9D8-45A4-8E40-A8DA76CB8E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{302CF2DE-2A83-48BD-85F9-8AC689B9B8DE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12555" yWindow="1395" windowWidth="16245" windowHeight="11415" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16800" windowHeight="6630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -20,26 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="49">
-  <si>
-    <t>    </t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>#</t>
   </si>
@@ -53,136 +39,130 @@
     <t>Érdemjegy</t>
   </si>
   <si>
-    <t>Bagó Bence</t>
-  </si>
-  <si>
-    <t>Balogh Roland</t>
-  </si>
-  <si>
-    <t>Bernát Bence Tamás</t>
-  </si>
-  <si>
-    <t>Budai Balázs</t>
-  </si>
-  <si>
-    <t>Farkas Dominika Eliza</t>
-  </si>
-  <si>
-    <t>Fendrik Bence</t>
-  </si>
-  <si>
-    <t>Kocsis Dominik Adrián</t>
-  </si>
-  <si>
-    <t>Körmöczi Martin Tibor</t>
-  </si>
-  <si>
-    <t>Lator Bence András</t>
-  </si>
-  <si>
-    <t>Magyar Máté</t>
-  </si>
-  <si>
-    <t>Nagy Szilvia Kamilla</t>
-  </si>
-  <si>
-    <t>Purák Anita</t>
-  </si>
-  <si>
-    <t>Sajtós Zoltán Viktor</t>
-  </si>
-  <si>
-    <t>Táborosi István Balázs</t>
-  </si>
-  <si>
-    <t>Zsóri Petra</t>
-  </si>
-  <si>
-    <t>Kis Attila Mihály</t>
-  </si>
-  <si>
-    <t>Kristof Gedeon</t>
-  </si>
-  <si>
-    <t>Kun-Szabó Zoltán</t>
-  </si>
-  <si>
-    <t>Annus Gergő István</t>
-  </si>
-  <si>
-    <t>Újvári Albert</t>
-  </si>
-  <si>
-    <t>Rada Bence</t>
-  </si>
-  <si>
-    <t>Galváts Richárd Ákos</t>
-  </si>
-  <si>
-    <t>sz1bagben@vasvari.org</t>
-  </si>
-  <si>
-    <t>sz1berben@vasvari.org</t>
-  </si>
-  <si>
-    <t>sz1annger@vasvari.org</t>
-  </si>
-  <si>
-    <t>sz1fardom@vasvari.org</t>
-  </si>
-  <si>
-    <t>sz1budbal@vasvari.org</t>
-  </si>
-  <si>
-    <t>sz1balrol@vasvari.org</t>
-  </si>
-  <si>
-    <t>sz1fenben@vasvari.org</t>
-  </si>
-  <si>
-    <t>sz1galric@vasvari.org</t>
-  </si>
-  <si>
-    <t>sz1kisatt@vasvari.org</t>
-  </si>
-  <si>
-    <t>sz1kocdom@vasvari.org</t>
-  </si>
-  <si>
-    <t>sz1kormar@vasvari.org</t>
-  </si>
-  <si>
-    <t>sz1kriged@vasvari.org</t>
-  </si>
-  <si>
-    <t>sz1kunzol@vasvari.org</t>
-  </si>
-  <si>
-    <t>sz1latben@vasvari.org</t>
-  </si>
-  <si>
-    <t>sz1magmat@vasvari.org</t>
-  </si>
-  <si>
-    <t>sz1nagszi@vasvari.org</t>
-  </si>
-  <si>
-    <t>sz1purani@vasvari.org</t>
-  </si>
-  <si>
-    <t>sz1radben@vasvari.org</t>
-  </si>
-  <si>
-    <t>sz1sajzol@vasvari.org</t>
-  </si>
-  <si>
-    <t>sz1tabist@vasvari.org</t>
-  </si>
-  <si>
-    <t>sz1ujvalb@vasvari.org</t>
-  </si>
-  <si>
-    <t>sz1zsopet@vasvari.org</t>
+    <t>szt2mulben@vasvari.org</t>
+  </si>
+  <si>
+    <t>szt2zakbal@vasvari.org</t>
+  </si>
+  <si>
+    <t>szt2somdan@vasvari.org</t>
+  </si>
+  <si>
+    <t>szt2mosjos@vasvari.org</t>
+  </si>
+  <si>
+    <t>szt2hodlaj@vasvari.org</t>
+  </si>
+  <si>
+    <t>szt2keklaj@vasvari.org</t>
+  </si>
+  <si>
+    <t>szt2vetmat@vasvari.org</t>
+  </si>
+  <si>
+    <t>szt2csonik@vasvari.org</t>
+  </si>
+  <si>
+    <t>szt2misnan@vasvari.org</t>
+  </si>
+  <si>
+    <t>szt2halpat@vasvari.org</t>
+  </si>
+  <si>
+    <t>szt2palpat@vasvari.org</t>
+  </si>
+  <si>
+    <t>szt2bacpet@vasvari.org</t>
+  </si>
+  <si>
+    <t>szt2makpet@vasvari.org</t>
+  </si>
+  <si>
+    <t>szt2mikric@vasvari.org</t>
+  </si>
+  <si>
+    <t>szt2gemsza@vasvari.org</t>
+  </si>
+  <si>
+    <t>szt2kehsza@vasvari.org</t>
+  </si>
+  <si>
+    <t>szt2poltam@vasvari.org</t>
+  </si>
+  <si>
+    <t>szt2peltam@vasvari.org</t>
+  </si>
+  <si>
+    <t>szt2szaviv@vasvari.org</t>
+  </si>
+  <si>
+    <t>szt2agoarm@vasvari.org</t>
+  </si>
+  <si>
+    <t>szt2bukarm@vasvari.org</t>
+  </si>
+  <si>
+    <t>Agócs Ármin</t>
+  </si>
+  <si>
+    <t>Bácskai Péter</t>
+  </si>
+  <si>
+    <t>Bukvity Ármin</t>
+  </si>
+  <si>
+    <t>Csorba Martin Nikolasz</t>
+  </si>
+  <si>
+    <t>Gémes Szabolcs</t>
+  </si>
+  <si>
+    <t>Halász Patrik</t>
+  </si>
+  <si>
+    <t>Hódi Lajos Gábor</t>
+  </si>
+  <si>
+    <t>Kehi Szabolcs</t>
+  </si>
+  <si>
+    <t>Kéki Lajos Máté</t>
+  </si>
+  <si>
+    <t>Makán Péter</t>
+  </si>
+  <si>
+    <t>Miklós Richárd Gábor</t>
+  </si>
+  <si>
+    <t>Miskolczi Nándor</t>
+  </si>
+  <si>
+    <t>Mösenlechner Josef Zoltán</t>
+  </si>
+  <si>
+    <t>Mulati Bence</t>
+  </si>
+  <si>
+    <t>Pálvölgyi Patrik</t>
+  </si>
+  <si>
+    <t>Péli Tamás</t>
+  </si>
+  <si>
+    <t>Somogyi Dániel</t>
+  </si>
+  <si>
+    <t>Szabó Vivien Liliána</t>
+  </si>
+  <si>
+    <t>Vetró Máté</t>
+  </si>
+  <si>
+    <t>Zakar Bálint</t>
+  </si>
+  <si>
+    <t>Polyákovich Tamás</t>
   </si>
 </sst>
 </file>
@@ -219,10 +199,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -537,417 +516,346 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetPr codeName="Munka1"/>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.140625" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.1796875" customWidth="1"/>
+    <col min="4" max="4" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
       <c r="D1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D2">
-        <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>4</v>
-      </c>
-      <c r="F2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" ref="D2:D23" ca="1" si="0">RANDBETWEEN(1,5)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>27</v>
       </c>
-      <c r="D3">
-        <f ca="1">RANDBETWEEN(1,5)</f>
+      <c r="C4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4">
+        <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="F3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4">
-        <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>3</v>
-      </c>
-      <c r="F4" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
         <v>28</v>
       </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="D5">
-        <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>1</v>
-      </c>
-      <c r="F5" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="D6">
-        <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>2</v>
-      </c>
-      <c r="F6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D7">
-        <f ca="1">RANDBETWEEN(1,5)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="F7" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D8">
-        <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>3</v>
-      </c>
-      <c r="F8" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
+        <v>32</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="D9">
-        <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>2</v>
-      </c>
-      <c r="F9" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D10">
-        <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>2</v>
-      </c>
-      <c r="F10" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" t="s">
-        <v>36</v>
+        <v>34</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="D11">
-        <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>1</v>
-      </c>
-      <c r="F11" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" t="s">
-        <v>37</v>
+        <v>35</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="D12">
-        <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>2</v>
-      </c>
-      <c r="F12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="D13">
-        <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>1</v>
-      </c>
-      <c r="F13" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" t="s">
-        <v>39</v>
+        <v>37</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="D14">
-        <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>2</v>
-      </c>
-      <c r="F14" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" t="s">
-        <v>40</v>
+        <v>38</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="D15">
-        <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>1</v>
-      </c>
-      <c r="F15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="D16">
-        <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>4</v>
-      </c>
-      <c r="F16" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D17">
-        <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>2</v>
-      </c>
-      <c r="F17" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="s">
-        <v>43</v>
+        <v>45</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="D18">
-        <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>2</v>
-      </c>
-      <c r="F18" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" t="s">
-        <v>44</v>
+        <v>41</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="D19">
-        <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>3</v>
-      </c>
-      <c r="F19" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" t="s">
-        <v>45</v>
+        <v>42</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="D20">
-        <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" t="s">
-        <v>46</v>
+        <v>43</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="D21">
-        <f ca="1">RANDBETWEEN(1,5)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" t="s">
-        <v>47</v>
+        <v>44</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="D22">
-        <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>19</v>
-      </c>
-      <c r="C23" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23">
-        <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>3</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D23">
+  <sortState ref="A2:D23">
     <sortCondition ref="B1:B23"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Eszközök/Forrás/2-14.b.xlsx
+++ b/Eszközök/Forrás/2-14.b.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\boros.bence\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{302CF2DE-2A83-48BD-85F9-8AC689B9B8DE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67DB7227-DF6B-4B3B-BA47-431499BCEC1A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16800" windowHeight="6630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>#</t>
   </si>
@@ -163,6 +163,12 @@
   </si>
   <si>
     <t>Polyákovich Tamás</t>
+  </si>
+  <si>
+    <t>Ótott-Kovács Tamás</t>
+  </si>
+  <si>
+    <t>szt2otokov@vasvari.org</t>
   </si>
 </sst>
 </file>
@@ -517,7 +523,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
@@ -551,7 +557,7 @@
       </c>
       <c r="D2">
         <f t="shared" ref="D2:D23" ca="1" si="0">RANDBETWEEN(1,5)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -566,7 +572,7 @@
       </c>
       <c r="D3">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -581,7 +587,7 @@
       </c>
       <c r="D4">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -596,7 +602,7 @@
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -611,7 +617,7 @@
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -626,7 +632,7 @@
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -641,7 +647,7 @@
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -701,7 +707,7 @@
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -716,7 +722,7 @@
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
@@ -731,7 +737,7 @@
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -746,7 +752,7 @@
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -754,14 +760,14 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -769,14 +775,14 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -784,14 +790,14 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -799,14 +805,14 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -814,14 +820,14 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -829,10 +835,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="0"/>
@@ -844,19 +850,34 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D22">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+      <c r="D23">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:D23">
-    <sortCondition ref="B1:B23"/>
+  <sortState ref="A2:D24">
+    <sortCondition ref="B1:B24"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
